--- a/student_data_cleaned.xlsx
+++ b/student_data_cleaned.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,22 +478,67 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>height_cm</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>height_cm</t>
+          <t>weight_kg</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>weight_kg</t>
+          <t>email_valid</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>email_valid</t>
+          <t>attendance_pct_scaled</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>homework_scaled</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>presentation_scaled</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>project_scaled</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>height_cm_scaled</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>weight_kg_scaled</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>city_Huangshi</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>city_Wuhan</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>gender_encoded</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>major_encoded</t>
         </is>
       </c>
     </row>
@@ -539,18 +584,43 @@
           <t>ali@example.com</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L2" t="n">
+        <v>173</v>
       </c>
       <c r="M2" t="n">
-        <v>173</v>
-      </c>
-      <c r="N2" t="n">
         <v>65</v>
       </c>
-      <c r="O2" t="b">
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.9829585394686032</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.2817879814705396</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.1729171253112709</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.01524276902124307</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.5120789674221283</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.2732173283642005</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -596,18 +666,43 @@
           <t>sara.li@example.com</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L3" t="n">
+        <v>165</v>
       </c>
       <c r="M3" t="n">
-        <v>165</v>
-      </c>
-      <c r="N3" t="n">
         <v>52</v>
       </c>
-      <c r="O3" t="b">
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3961176203828702</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8101404467277998</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.4034732923929641</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.4725258396585124</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.6365093707209645</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.9952916961838745</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -653,19 +748,44 @@
           <t>zhang.wei@example.com</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Huangshi</t>
-        </is>
+      <c r="L4" t="n">
+        <v>178</v>
       </c>
       <c r="M4" t="n">
-        <v>178</v>
-      </c>
-      <c r="N4" t="n">
         <v>70</v>
       </c>
-      <c r="O4" t="b">
-        <v>1</v>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.423089228782903</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.33849291198506</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.9798637100971991</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.158450445614416</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.229946678761561</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.7611054147288446</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -710,19 +830,44 @@
           <t>fatima.noor@example.com</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Huangshi</t>
-        </is>
+      <c r="L5" t="n">
+        <v>160</v>
       </c>
       <c r="M5" t="n">
-        <v>160</v>
-      </c>
-      <c r="N5" t="n">
         <v>50</v>
       </c>
-      <c r="O5" t="b">
-        <v>1</v>
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1760522757257203</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.7749169490439807</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.1729171253112709</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.6706818369346609</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-1.354377082060398</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1.190446930729732</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -767,18 +912,43 @@
           <t>chen.yu@example.com</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L6" t="n">
+        <v>181</v>
       </c>
       <c r="M6" t="n">
-        <v>181</v>
-      </c>
-      <c r="N6" t="n">
         <v>75</v>
       </c>
-      <c r="O6" t="b">
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-1.364405136874329</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-1.303269414301241</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1.325697960719741</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1.12796490757193</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.660667305565221</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.248993501093489</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -824,19 +994,44 @@
           <t>bilal@example.com</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L7" t="n">
+        <v>176</v>
       </c>
       <c r="M7" t="n">
-        <v>176</v>
-      </c>
-      <c r="N7" t="n">
         <v>72</v>
       </c>
-      <c r="O7" t="b">
-        <v>1</v>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1760522757257203</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.2817879814705396</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.749307543015506</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.2438843043398777</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.9427995942257882</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.9562606492747023</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -881,19 +1076,44 @@
           <t>liu.mei@example.com</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Huangshi</t>
-        </is>
+      <c r="L8" t="n">
+        <v>158</v>
       </c>
       <c r="M8" t="n">
-        <v>158</v>
-      </c>
-      <c r="N8" t="n">
         <v>47</v>
       </c>
-      <c r="O8" t="b">
-        <v>1</v>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.3374335284742961</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.2817879814705396</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4034732923929641</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.2133987662973916</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-1.641524166596171</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-1.483179782548519</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -938,19 +1158,44 @@
           <t>ayesha@example.com</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Huangshi</t>
-        </is>
+      <c r="L9" t="n">
+        <v>164</v>
       </c>
       <c r="M9" t="n">
-        <v>164</v>
-      </c>
-      <c r="N9" t="n">
         <v>55</v>
       </c>
-      <c r="O9" t="b">
-        <v>1</v>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.83624830969717</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.33849291198506</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.556254127801434</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.387091980933051</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.7800829129888511</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.7025588443650879</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -995,18 +1240,43 @@
           <t>wang.jun@example.com</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L10" t="n">
+        <v>175</v>
       </c>
       <c r="M10" t="n">
-        <v>175</v>
-      </c>
-      <c r="N10" t="n">
         <v>68</v>
       </c>
-      <c r="O10" t="b">
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.951246055960062</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-1.831621879558501</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.325697960719741</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-1.813889513527834</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.7992260519579016</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.5659501801829869</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1052,19 +1322,44 @@
           <t>hassan@example.com</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Huangshi</t>
-        </is>
+      <c r="L11" t="n">
+        <v>172</v>
       </c>
       <c r="M11" t="n">
-        <v>172</v>
-      </c>
-      <c r="N11" t="n">
         <v>80</v>
       </c>
-      <c r="O11" t="b">
-        <v>1</v>
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-2.538086975045795</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-2.359974344815761</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-1.902088378423976</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-2.271172584165104</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.3685054251542418</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.736881587458133</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1109,19 +1404,44 @@
           <t>lina@example.com</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L12" t="n">
+        <v>162</v>
       </c>
       <c r="M12" t="n">
-        <v>162</v>
-      </c>
-      <c r="N12" t="n">
         <v>51</v>
       </c>
-      <c r="O12" t="b">
-        <v>1</v>
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.5428278501543035</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.8101404467277998</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.9798637100971991</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.7011673749771471</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-1.067229997524624</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-1.092869313456803</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1166,18 +1486,43 @@
           <t>omar@example.com</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L13" t="n">
+        <v>180</v>
       </c>
       <c r="M13" t="n">
-        <v>180</v>
-      </c>
-      <c r="N13" t="n">
         <v>78</v>
       </c>
-      <c r="O13" t="b">
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.1907232987028628</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.2465644837867206</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.749307543015506</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.4420403016160263</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.517093763297335</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.541726352912275</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1223,19 +1568,44 @@
           <t>zhou.min@example.com</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Huangshi</t>
-        </is>
+      <c r="L14" t="n">
+        <v>166</v>
       </c>
       <c r="M14" t="n">
-        <v>166</v>
-      </c>
-      <c r="N14" t="n">
         <v>54</v>
       </c>
-      <c r="O14" t="b">
-        <v>1</v>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.249407390611437</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.2817879814705396</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.1729171253112709</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2438843043398777</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.4929358284530779</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.8001364616380168</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1280,19 +1650,44 @@
           <t>hina@example.com</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Huangshi</t>
-        </is>
+      <c r="L15" t="n">
+        <v>163</v>
       </c>
       <c r="M15" t="n">
-        <v>163</v>
-      </c>
-      <c r="N15" t="n">
         <v>53</v>
       </c>
-      <c r="O15" t="b">
-        <v>1</v>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.6895380799257368</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.8101404467277998</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.4034732923929641</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.9298089102957817</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.9236564552567378</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.8977140789109456</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1337,18 +1732,43 @@
           <t>wutao@example.com</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L16" t="n">
+        <v>168</v>
       </c>
       <c r="M16" t="n">
-        <v>168</v>
-      </c>
-      <c r="N16" t="n">
         <v>73</v>
       </c>
-      <c r="O16" t="b">
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.6308539880171626</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.7749169490439807</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1.325697960719741</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.8993233722532956</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.2057887439173047</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.053838266547631</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1394,19 +1814,44 @@
           <t>noor@example.com</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Huangshi</t>
-        </is>
+      <c r="L17" t="n">
+        <v>167</v>
       </c>
       <c r="M17" t="n">
-        <v>167</v>
-      </c>
-      <c r="N17" t="n">
         <v>64</v>
       </c>
-      <c r="O17" t="b">
-        <v>1</v>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-1.070984677331462</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-1.303269414301241</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-1.902088378423976</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-1.356606442890565</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.3493622861851913</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.1756397110912716</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1451,19 +1896,44 @@
           <t>sun.lei@example.com</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L18" t="n">
+        <v>179</v>
       </c>
       <c r="M18" t="n">
-        <v>179</v>
-      </c>
-      <c r="N18" t="n">
         <v>69</v>
       </c>
-      <c r="O18" t="b">
-        <v>1</v>
+      <c r="N18" t="b">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.27637899901147</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.33849291198506</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.9798637100971991</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.158450445614416</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.373520221029448</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.6635277974559158</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1508,18 +1978,43 @@
           <t>maryam@example.com</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L19" t="n">
+        <v>161</v>
       </c>
       <c r="M19" t="n">
-        <v>161</v>
-      </c>
-      <c r="N19" t="n">
         <v>50</v>
       </c>
-      <c r="O19" t="b">
+      <c r="N19" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.04401306893142956</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.2465644837867206</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.4034732923929641</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.01524276902124307</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-1.210803539792511</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1.190446930729732</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1565,19 +2060,44 @@
           <t>xu.chen@example.com</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Huangshi</t>
-        </is>
+      <c r="L20" t="n">
+        <v>174</v>
       </c>
       <c r="M20" t="n">
-        <v>174</v>
-      </c>
-      <c r="N20" t="n">
         <v>66</v>
       </c>
-      <c r="O20" t="b">
-        <v>1</v>
+      <c r="N20" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.9242744475600292</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.7749169490439807</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.749307543015506</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.6706818369346609</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.655652509690015</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.3707949456371293</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1622,19 +2142,44 @@
           <t>ahmed.saeed@example.com</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Huangshi</t>
-        </is>
+      <c r="L21" t="n">
+        <v>177</v>
       </c>
       <c r="M21" t="n">
-        <v>177</v>
-      </c>
-      <c r="N21" t="n">
         <v>71</v>
       </c>
-      <c r="O21" t="b">
-        <v>1</v>
+      <c r="N21" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.4841437582457294</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.2817879814705396</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-1.325697960719741</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.4420403016160263</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.086373136493675</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.8586830320017735</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1677,18 +2222,43 @@
           <t>lin.fang@example.com</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L22" t="n">
+        <v>159</v>
       </c>
       <c r="M22" t="n">
-        <v>159</v>
-      </c>
-      <c r="N22" t="n">
         <v>48</v>
       </c>
-      <c r="O22" t="b">
+      <c r="N22" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.129668769240036</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.8101404467277998</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.556254127801434</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.387091980933051</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-1.497950624328284</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-1.38560216527559</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1734,19 +2304,44 @@
           <t>usman@example.com</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L23" t="n">
+        <v>171</v>
       </c>
       <c r="M23" t="n">
-        <v>171</v>
-      </c>
-      <c r="N23" t="n">
         <v>67</v>
       </c>
-      <c r="O23" t="b">
-        <v>1</v>
+      <c r="N23" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.1026971608400037</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.2817879814705396</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.1729171253112709</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.2438843043398777</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.2249318828863552</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.4683725629100581</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1791,19 +2386,44 @@
           <t>gao.rui@example.com</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Huangshi</t>
-        </is>
+      <c r="L24" t="n">
+        <v>168</v>
       </c>
       <c r="M24" t="n">
-        <v>168</v>
-      </c>
-      <c r="N24" t="n">
         <v>56</v>
       </c>
-      <c r="O24" t="b">
-        <v>1</v>
+      <c r="N24" t="b">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.3961176203828702</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.2817879814705396</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.4034732923929641</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.4725258396585124</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.2057887439173047</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.6049812270921591</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1848,18 +2468,43 @@
           <t>sana@example.com</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Huangshi</t>
-        </is>
+      <c r="L25" t="n">
+        <v>164</v>
       </c>
       <c r="M25" t="n">
-        <v>164</v>
-      </c>
-      <c r="N25" t="n">
         <v>54</v>
       </c>
-      <c r="O25" t="b">
+      <c r="N25" t="b">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.6895380799257368</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.8101404467277998</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.9798637100971991</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9298089102957817</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.7800829129888511</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.8001364616380168</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1905,19 +2550,44 @@
           <t>ma.long@example.com</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L26" t="n">
+        <v>182</v>
       </c>
       <c r="M26" t="n">
-        <v>182</v>
-      </c>
-      <c r="N26" t="n">
         <v>82</v>
       </c>
-      <c r="O26" t="b">
-        <v>1</v>
+      <c r="N26" t="b">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.657825596417196</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.831621879558501</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.4034732923929641</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-1.5852479782092</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.804240847833108</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.932036822003991</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1962,19 +2632,44 @@
           <t>iqra@example.com</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L27" t="n">
+        <v>166</v>
       </c>
       <c r="M27" t="n">
-        <v>166</v>
-      </c>
-      <c r="N27" t="n">
         <v>57</v>
       </c>
-      <c r="O27" t="b">
-        <v>1</v>
+      <c r="N27" t="b">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.569799458554336</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.33849291198506</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.556254127801434</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.615733516251686</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.4929358284530779</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.5074036098192303</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2019,18 +2714,43 @@
           <t>he.ping@example.com</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Huangshi</t>
-        </is>
+      <c r="L28" t="n">
+        <v>170</v>
       </c>
       <c r="M28" t="n">
-        <v>170</v>
-      </c>
-      <c r="N28" t="n">
         <v>64</v>
       </c>
-      <c r="O28" t="b">
+      <c r="N28" t="b">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.7775642177885959</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-0.7749169490439807</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.749307543015506</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-0.8993233722532956</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.08135834061846854</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.1756397110912716</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2076,19 +2796,44 @@
           <t>zara@example.com</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Huangshi</t>
-        </is>
+      <c r="L29" t="n">
+        <v>165</v>
       </c>
       <c r="M29" t="n">
-        <v>165</v>
-      </c>
-      <c r="N29" t="n">
         <v>53</v>
       </c>
-      <c r="O29" t="b">
-        <v>1</v>
+      <c r="N29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.04401306893142956</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-0.2465644837867206</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.4034732923929641</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.01524276902124307</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-0.6365093707209645</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-0.8977140789109456</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2133,19 +2878,44 @@
           <t>tang.jie@example.com</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L30" t="n">
+        <v>176</v>
       </c>
       <c r="M30" t="n">
-        <v>176</v>
-      </c>
-      <c r="N30" t="n">
         <v>70</v>
       </c>
-      <c r="O30" t="b">
-        <v>1</v>
+      <c r="N30" t="b">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.5428278501543035</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.2817879814705396</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.9798637100971991</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.7011673749771471</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.9427995942257882</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.7611054147288446</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2190,18 +2960,43 @@
           <t>amna@example.com</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Wuhan</t>
-        </is>
+      <c r="L31" t="n">
+        <v>163</v>
       </c>
       <c r="M31" t="n">
-        <v>163</v>
-      </c>
-      <c r="N31" t="n">
         <v>52</v>
       </c>
-      <c r="O31" t="b">
+      <c r="N31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.83624830969717</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.8101404467277998</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.4034732923929641</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.7011673749771471</v>
+      </c>
+      <c r="S31" t="n">
+        <v>-0.9236564552567378</v>
+      </c>
+      <c r="T31" t="n">
+        <v>-0.9952916961838745</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
         <v>1</v>
       </c>
     </row>
